--- a/Conteos_Calidad.xlsx
+++ b/Conteos_Calidad.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Viual_Studio_V\Tourism_Ontology_Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1613DD08-36D4-451D-A7F5-0CF00262325A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF04902-E61F-4122-A388-938866835725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7941AEB6-EA9D-4938-804A-08A062991D30}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pamplona_UTE" sheetId="1" r:id="rId1"/>
+    <sheet name="Pamplona_Use Case" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
   <si>
     <t>=============================</t>
   </si>
   <si>
-    <t>RESUMEN</t>
-  </si>
-  <si>
     <t>==============================</t>
   </si>
   <si>
@@ -225,13 +222,212 @@
   </si>
   <si>
     <t>Tavern: 1 (0.11%)</t>
+  </si>
+  <si>
+    <t>================================================================================</t>
+  </si>
+  <si>
+    <t>Entidades con imagen:        1369</t>
+  </si>
+  <si>
+    <t>Entidades con coordenadas:   80</t>
+  </si>
+  <si>
+    <t>DESGLOSE POR CLASE</t>
+  </si>
+  <si>
+    <t>Clase                                  Total   Con imagen   Con coords</t>
+  </si>
+  <si>
+    <t>--------------------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>Monument                                 394          393            5</t>
+  </si>
+  <si>
+    <t>AccommodationEstablishment                49           49            4</t>
+  </si>
+  <si>
+    <t>Castle                                    41           41            1</t>
+  </si>
+  <si>
+    <t>Cathedral                                 41           40            4</t>
+  </si>
+  <si>
+    <t>FoodEstablishment                         30           30            0</t>
+  </si>
+  <si>
+    <t>Museum                                    26           26            1</t>
+  </si>
+  <si>
+    <t>Basilica                                  24           24            1</t>
+  </si>
+  <si>
+    <t>HistoricalOrCulturalResource              20           20            0</t>
+  </si>
+  <si>
+    <t>Church                                    19           18            3</t>
+  </si>
+  <si>
+    <t>Place                                     19           18            2</t>
+  </si>
+  <si>
+    <t>TownHall                                  17           17            1</t>
+  </si>
+  <si>
+    <t>Square                                    16           16            2</t>
+  </si>
+  <si>
+    <t>Alcazar                                    9            9            0</t>
+  </si>
+  <si>
+    <t>Concept                                    6            6            0</t>
+  </si>
+  <si>
+    <t>ArcheologicalSite                          5            5            0</t>
+  </si>
+  <si>
+    <t>Chapel                                     4            4            0</t>
+  </si>
+  <si>
+    <t>Event                                      4            4            0</t>
+  </si>
+  <si>
+    <t>EventOrganisationCompany                   3            3            0</t>
+  </si>
+  <si>
+    <t>PublicService                              3            3            0</t>
+  </si>
+  <si>
+    <t>EventAttendanceFacility                    2            2            0</t>
+  </si>
+  <si>
+    <t>ExhibitionHall                             2            2            0</t>
+  </si>
+  <si>
+    <t>TransportInfrastructure                    2            2            0</t>
+  </si>
+  <si>
+    <t>DestinationExperience                      1            1            0</t>
+  </si>
+  <si>
+    <t>EducationalCenter                          1            1            0</t>
+  </si>
+  <si>
+    <t>NaturalFormation                           1            1            0</t>
+  </si>
+  <si>
+    <t>RetailAndFashion                           1            1            0</t>
+  </si>
+  <si>
+    <t>Stadium                                    1            1            0</t>
+  </si>
+  <si>
+    <t>TourismService                             1            1            0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Entidades detectadas ?? :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        1380</t>
+    </r>
+  </si>
+  <si>
+    <t>Thing     ?????    ( UNKNOWN)                           669          660           58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2.1 PARAMETRIZACION DEL SISTEMA  DEPENDIENTE DEL CRAWLER ( CONTENIDO DISPONIBLE )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2.2 PARAMETRIZACION DEL SISTEMA DEPENDIENTE DEL SCRAPPER ( CANDIDATOS A ENTIDAD TURISTICA )</t>
+  </si>
+  <si>
+    <t>1) QUE ES UNA ENTIDAD TURISTICA ?</t>
+  </si>
+  <si>
+    <t>2) COMO SE DETECTA UNA ENTIDAD TURISTICA A PARTIR DE UNA DESCRIPCION DE TEXTO?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     2.1.1 Si aquí metemos un primer nivel de filttrado a partir de lo que se define como contenido turistico mejor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     2.2.1 Filttrado definintivo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     2.2.3 Deduplicacion  de entidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2.3 CLASIFICACION ONTOLOGICA (388 CATEGORIAS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     2.3. Sumamente dificil que haya entidades desclasificadas ( 388 Categorias Ontologicas )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            2.3.1 Si en este punto han entrado candidatos "fake", entonces no deberia ser posible clasificarlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            2.3.2 La hipótesis mas negativa es que hayan entrado candidatos incorrectos y se clasifiquen ontológicamentte</t>
+  </si>
+  <si>
+    <t>CONCLUSIONES …</t>
+  </si>
+  <si>
+    <r>
+      <t>RESUMEN 1 NOTA (SUBJETIVA)  :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BIEN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>RESUMEN GENERAL 2 ( 1 TESTEO de múltipes) :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INSUFICIENTE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">     2.2.2 Normalizacion del identificador de entidades</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,13 +435,87 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -260,8 +530,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,343 +882,558 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D30278-7BD8-413F-B88D-1955FDF4385C}">
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.7265625" customWidth="1"/>
+    <col min="1" max="1" width="35.90625" customWidth="1"/>
+    <col min="2" max="2" width="1.08984375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="82.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.1796875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="82.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="C37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9374c06d-764e-4cac-ad94-de61fd94590c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009BA0772FA317E3499A8C648E0D4BE956" ma:contentTypeVersion="5" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="885e7d9bf587fa5bf50ea6fd981483d0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9374c06d-764e-4cac-ad94-de61fd94590c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff29ad8e91a4f46e9e751c7b2db2fbca" ns3:_="">
     <xsd:import namespace="9374c06d-764e-4cac-ad94-de61fd94590c"/>
@@ -1082,24 +1583,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C9C5DD-5580-44A7-B42C-809690004339}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9374c06d-764e-4cac-ad94-de61fd94590c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9374c06d-764e-4cac-ad94-de61fd94590c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87F41FF-6141-4030-914B-EB43008C9CCD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA28BE9-D52D-4CCD-88CB-44B1BF5ED774}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1115,28 +1623,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87F41FF-6141-4030-914B-EB43008C9CCD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C9C5DD-5580-44A7-B42C-809690004339}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9374c06d-764e-4cac-ad94-de61fd94590c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>